--- a/Marketing.Mvc/DadosApp/Relatorio/Relatório de Envio de Extratos de Incidência_janeiro2026.xlsx
+++ b/Marketing.Mvc/DadosApp/Relatorio/Relatório de Envio de Extratos de Incidência_janeiro2026.xlsx
@@ -94,6 +94,27 @@
   </x:si>
   <x:si>
     <x:t>Os CNPS´s marcados com esta cor não constam no envio do mês anterior.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/03/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOMINOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CACHAMBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15442958000100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5511977515914</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INQUEUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
   </x:si>
 </x:sst>
 </file>
@@ -1070,13 +1091,27 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:27" ht="16.5" customHeight="1">
-      <x:c r="A7" s="20"/>
-      <x:c r="B7" s="21"/>
-      <x:c r="C7" s="22"/>
-      <x:c r="D7" s="23"/>
-      <x:c r="E7" s="24"/>
-      <x:c r="F7" s="24"/>
-      <x:c r="G7" s="37"/>
+      <x:c r="A7" s="20" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B7" s="21" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C7" s="22" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D7" s="23" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E7" s="24" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F7" s="24" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G7" s="37" t="s">
+        <x:v>29</x:v>
+      </x:c>
       <x:c r="H7" s="25"/>
       <x:c r="I7" s="25"/>
       <x:c r="J7" s="25"/>
@@ -1098,7 +1133,7 @@
       <x:c r="Z7" s="25"/>
       <x:c r="AA7" s="25"/>
     </x:row>
-    <x:row r="8" spans="1:27" ht="16.5" customHeight="1">
+    <x:row r="8" spans="1:27" ht="15" customHeight="1">
       <x:c r="A8" s="20"/>
       <x:c r="B8" s="21"/>
       <x:c r="C8" s="22"/>
@@ -1127,57 +1162,71 @@
       <x:c r="Z8" s="25"/>
       <x:c r="AA8" s="25"/>
     </x:row>
-    <x:row r="9" spans="1:27" ht="16.5" customHeight="1">
-      <x:c r="A9" s="13"/>
-      <x:c r="B9" s="14"/>
-      <x:c r="C9" s="15"/>
-      <x:c r="D9" s="16"/>
-      <x:c r="E9" s="15"/>
-      <x:c r="F9" s="15"/>
-      <x:c r="G9" s="38"/>
-    </x:row>
-    <x:row r="10" spans="1:27" ht="15.75" customHeight="1">
-      <x:c r="A10" s="4"/>
-      <x:c r="B10" s="4"/>
-      <x:c r="C10" s="4"/>
-      <x:c r="D10" s="5"/>
-      <x:c r="E10" s="4"/>
-      <x:c r="F10" s="4"/>
-      <x:c r="G10" s="17"/>
+    <x:row r="9" spans="1:27">
+      <x:c r="A9" s="20"/>
+      <x:c r="B9" s="21"/>
+      <x:c r="C9" s="22"/>
+      <x:c r="D9" s="23"/>
+      <x:c r="E9" s="24"/>
+      <x:c r="F9" s="24"/>
+      <x:c r="G9" s="37"/>
+      <x:c r="H9" s="25"/>
+      <x:c r="I9" s="25"/>
+      <x:c r="J9" s="25"/>
+      <x:c r="K9" s="25"/>
+      <x:c r="L9" s="25"/>
+      <x:c r="M9" s="25"/>
+      <x:c r="N9" s="25"/>
+      <x:c r="O9" s="25"/>
+      <x:c r="P9" s="25"/>
+      <x:c r="Q9" s="25"/>
+      <x:c r="R9" s="25"/>
+      <x:c r="S9" s="25"/>
+      <x:c r="T9" s="25"/>
+      <x:c r="U9" s="25"/>
+      <x:c r="V9" s="25"/>
+      <x:c r="W9" s="25"/>
+      <x:c r="X9" s="25"/>
+      <x:c r="Y9" s="25"/>
+      <x:c r="Z9" s="25"/>
+      <x:c r="AA9" s="25"/>
+    </x:row>
+    <x:row r="10" spans="1:27" ht="16.5" customHeight="1">
+      <x:c r="A10" s="13"/>
+      <x:c r="B10" s="14"/>
+      <x:c r="C10" s="15"/>
+      <x:c r="D10" s="16"/>
+      <x:c r="E10" s="15"/>
+      <x:c r="F10" s="15"/>
+      <x:c r="G10" s="38"/>
     </x:row>
     <x:row r="11" spans="1:27" ht="15.75" customHeight="1">
-      <x:c r="A11" s="25"/>
-      <x:c r="B11" s="25"/>
-      <x:c r="C11" s="25"/>
-      <x:c r="D11" s="26"/>
-      <x:c r="E11" s="25"/>
-      <x:c r="F11" s="25"/>
-      <x:c r="G11" s="18"/>
-    </x:row>
-    <x:row r="12" spans="1:27" ht="22.5" customHeight="1">
-      <x:c r="A12" s="39" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B12" s="39">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" s="36" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D12" s="36"/>
-      <x:c r="E12" s="36"/>
-      <x:c r="F12" s="36"/>
-      <x:c r="G12" s="36"/>
+      <x:c r="A11" s="4"/>
+      <x:c r="B11" s="4"/>
+      <x:c r="C11" s="4"/>
+      <x:c r="D11" s="5"/>
+      <x:c r="E11" s="4"/>
+      <x:c r="F11" s="4"/>
+      <x:c r="G11" s="17"/>
+    </x:row>
+    <x:row r="12" spans="1:27" ht="15.75" customHeight="1">
+      <x:c r="A12" s="25"/>
+      <x:c r="B12" s="25"/>
+      <x:c r="C12" s="25"/>
+      <x:c r="D12" s="26"/>
+      <x:c r="E12" s="25"/>
+      <x:c r="F12" s="25"/>
+      <x:c r="G12" s="18"/>
     </x:row>
     <x:row r="13" spans="1:27" ht="22.5" customHeight="1">
       <x:c r="A13" s="39" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B13" s="39">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="36" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D13" s="36"/>
       <x:c r="E13" s="36"/>
@@ -1186,48 +1235,59 @@
     </x:row>
     <x:row r="14" spans="1:27" ht="22.5" customHeight="1">
       <x:c r="A14" s="39" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="39">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="36" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D14" s="36"/>
       <x:c r="E14" s="36"/>
       <x:c r="F14" s="36"/>
       <x:c r="G14" s="36"/>
     </x:row>
-    <x:row r="15" spans="1:27" ht="60" customHeight="1">
+    <x:row r="15" spans="1:27" ht="22.5" customHeight="1">
       <x:c r="A15" s="39" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B15" s="39">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="36" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D15" s="36"/>
       <x:c r="E15" s="36"/>
       <x:c r="F15" s="36"/>
       <x:c r="G15" s="36"/>
     </x:row>
-    <x:row r="16" spans="1:27" ht="30" customHeight="1">
-      <x:c r="A16" s="50"/>
-      <x:c r="B16" s="39"/>
+    <x:row r="16" spans="1:27" ht="60" customHeight="1">
+      <x:c r="A16" s="39" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B16" s="39">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="C16" s="36" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D16" s="36"/>
       <x:c r="E16" s="36"/>
       <x:c r="F16" s="36"/>
       <x:c r="G16" s="36"/>
     </x:row>
-    <x:row r="17" spans="1:27" ht="15.75" customHeight="1">
-      <x:c r="D17" s="27"/>
-      <x:c r="G17" s="18"/>
+    <x:row r="17" spans="1:27" ht="30" customHeight="1">
+      <x:c r="A17" s="50"/>
+      <x:c r="B17" s="39"/>
+      <x:c r="C17" s="36" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D17" s="36"/>
+      <x:c r="E17" s="36"/>
+      <x:c r="F17" s="36"/>
+      <x:c r="G17" s="36"/>
     </x:row>
     <x:row r="18" spans="1:27" ht="15.75" customHeight="1">
       <x:c r="D18" s="27"/>
@@ -2027,6 +2087,7 @@
     </x:row>
     <x:row r="217" spans="1:27" ht="15.75" customHeight="1">
       <x:c r="D217" s="27"/>
+      <x:c r="G217" s="18"/>
     </x:row>
     <x:row r="218" spans="1:27" ht="15.75" customHeight="1">
       <x:c r="D218" s="27"/>
@@ -4052,6 +4113,9 @@
     </x:row>
     <x:row r="892" spans="1:27" ht="15.75" customHeight="1">
       <x:c r="D892" s="27"/>
+    </x:row>
+    <x:row r="893" spans="1:27" ht="15.75" customHeight="1">
+      <x:c r="D893" s="27"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="10">
@@ -4060,18 +4124,18 @@
     <x:mergeCell ref="B2:F2"/>
     <x:mergeCell ref="B3:F3"/>
     <x:mergeCell ref="B4:F4"/>
-    <x:mergeCell ref="C12:G12"/>
     <x:mergeCell ref="C13:G13"/>
     <x:mergeCell ref="C14:G14"/>
     <x:mergeCell ref="C15:G15"/>
     <x:mergeCell ref="C16:G16"/>
+    <x:mergeCell ref="C17:G17"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="D7:D8">
+  <x:conditionalFormatting sqref="D7:D9">
     <x:cfRule type="expression" dxfId="0" priority="1" operator="equal">
       <x:formula>H7=1</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="G1:G11 G17:G1048576">
+  <x:conditionalFormatting sqref="G1:G12 G18:G1048576">
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="UNDELIVERED">
       <x:formula>NOT(ISERROR(SEARCH("UNDELIVERED",G1)))</x:formula>
     </x:cfRule>
